--- a/artfynd/A 53351-2024 artfynd.xlsx
+++ b/artfynd/A 53351-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136455475</v>
       </c>
       <c r="B2" t="n">
-        <v>91111</v>
+        <v>91113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136455473</v>
       </c>
       <c r="B3" t="n">
-        <v>93425</v>
+        <v>93428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>136455474</v>
       </c>
       <c r="B5" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>136455479</v>
       </c>
       <c r="B6" t="n">
-        <v>90870</v>
+        <v>90872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 53351-2024 artfynd.xlsx
+++ b/artfynd/A 53351-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136455473</v>
       </c>
       <c r="B3" t="n">
-        <v>93428</v>
+        <v>93429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>136455474</v>
       </c>
       <c r="B5" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 53351-2024 artfynd.xlsx
+++ b/artfynd/A 53351-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136455475</v>
       </c>
       <c r="B2" t="n">
-        <v>91113</v>
+        <v>91115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136455473</v>
       </c>
       <c r="B3" t="n">
-        <v>93429</v>
+        <v>93434</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>136455474</v>
       </c>
       <c r="B5" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>136455479</v>
       </c>
       <c r="B6" t="n">
-        <v>90872</v>
+        <v>90874</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136455478</v>
       </c>
       <c r="B7" t="n">
-        <v>78478</v>
+        <v>78480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>136455477</v>
       </c>
       <c r="B8" t="n">
-        <v>79497</v>
+        <v>79499</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 53351-2024 artfynd.xlsx
+++ b/artfynd/A 53351-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136455475</v>
       </c>
       <c r="B2" t="n">
-        <v>91115</v>
+        <v>91117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136455473</v>
       </c>
       <c r="B3" t="n">
-        <v>93434</v>
+        <v>93436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>136455474</v>
       </c>
       <c r="B5" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>136455479</v>
       </c>
       <c r="B6" t="n">
-        <v>90874</v>
+        <v>90876</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 53351-2024 artfynd.xlsx
+++ b/artfynd/A 53351-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136455475</v>
       </c>
       <c r="B2" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136455473</v>
       </c>
       <c r="B3" t="n">
-        <v>93436</v>
+        <v>93438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>136455474</v>
       </c>
       <c r="B5" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>136455479</v>
       </c>
       <c r="B6" t="n">
-        <v>90876</v>
+        <v>90878</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>136455477</v>
       </c>
       <c r="B8" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 53351-2024 artfynd.xlsx
+++ b/artfynd/A 53351-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136455475</v>
       </c>
       <c r="B2" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136455473</v>
       </c>
       <c r="B3" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>136455474</v>
       </c>
       <c r="B5" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>136455479</v>
       </c>
       <c r="B6" t="n">
-        <v>90878</v>
+        <v>90880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136455478</v>
       </c>
       <c r="B7" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>136455477</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 53351-2024 artfynd.xlsx
+++ b/artfynd/A 53351-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136455475</v>
       </c>
       <c r="B2" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136455473</v>
       </c>
       <c r="B3" t="n">
-        <v>93440</v>
+        <v>93441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>136455474</v>
       </c>
       <c r="B5" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>136455479</v>
       </c>
       <c r="B6" t="n">
-        <v>90880</v>
+        <v>90881</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>136455478</v>
       </c>
       <c r="B7" t="n">
-        <v>78482</v>
+        <v>78483</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>136455477</v>
       </c>
       <c r="B8" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 53351-2024 artfynd.xlsx
+++ b/artfynd/A 53351-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136455475</v>
       </c>
       <c r="B2" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136455473</v>
       </c>
       <c r="B3" t="n">
-        <v>93441</v>
+        <v>93447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>136455474</v>
       </c>
       <c r="B5" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>136455479</v>
       </c>
       <c r="B6" t="n">
-        <v>90881</v>
+        <v>90887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
